--- a/artfynd/A 49519-2022 artfynd.xlsx
+++ b/artfynd/A 49519-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49519-2022 artfynd.xlsx
+++ b/artfynd/A 49519-2022 artfynd.xlsx
@@ -2459,7 +2459,7 @@
         <v>110875620</v>
       </c>
       <c r="B17" t="n">
-        <v>56398</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520928.8200006362</v>
+        <v>520929</v>
       </c>
       <c r="R17" t="n">
-        <v>6920108.018878634</v>
+        <v>6920108</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2537,19 +2537,9 @@
           <t>2023-07-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-07-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">

--- a/artfynd/A 49519-2022 artfynd.xlsx
+++ b/artfynd/A 49519-2022 artfynd.xlsx
@@ -2463,7 +2463,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">

--- a/artfynd/A 49519-2022 artfynd.xlsx
+++ b/artfynd/A 49519-2022 artfynd.xlsx
@@ -2459,7 +2459,7 @@
         <v>110875620</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 49519-2022 artfynd.xlsx
+++ b/artfynd/A 49519-2022 artfynd.xlsx
@@ -2459,7 +2459,7 @@
         <v>110875620</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
